--- a/account_master.xlsx
+++ b/account_master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCAF047-0AEF-454C-93BE-8332C960ECF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7E7D16-83D3-4939-A084-037522457F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="계정마스터" sheetId="1" r:id="rId1"/>
@@ -19,11 +19,6 @@
     <sheet name="원본데이터" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -136,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="188">
   <si>
     <t>광고 계정 마스터 (네이버/메타 공용)</t>
   </si>
@@ -689,6 +684,21 @@
   </si>
   <si>
     <t>핵이득마켓</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>대성소파</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국금거래소</t>
+  </si>
+  <si>
+    <t>한국금거래소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>대성소파</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -822,7 +832,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -867,9 +877,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -882,6 +889,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1005,11 +1016,61 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>257175</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1045C7F9-BDCD-ED0B-0DB8-915D314D4623}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1188,7 +1249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1206,55 +1267,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -3897,10 +3958,10 @@
       <c r="A70" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="B70" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="C70" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D70" s="6" t="s">
@@ -3915,7 +3976,7 @@
       <c r="G70">
         <v>3492778</v>
       </c>
-      <c r="J70" s="17" t="s">
+      <c r="J70" s="16" t="s">
         <v>182</v>
       </c>
       <c r="K70" s="6" t="s">
@@ -3960,6 +4021,70 @@
         <v>23</v>
       </c>
       <c r="M71" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>121</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G72">
+        <v>530852</v>
+      </c>
+      <c r="J72" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
+        <v>185</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73">
+        <v>122788</v>
+      </c>
+      <c r="J73" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M73" s="6" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3971,7 +4096,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="D5:D1000 G71 L5:L1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="L5:L1000 G71 D5:D1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E5:E1000" xr:uid="{00000000-0002-0000-0000-000001000000}">

--- a/account_master.xlsx
+++ b/account_master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\OneDrive\바탕 화면\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7E7D16-83D3-4939-A084-037522457F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7E785BC-40B8-4DA2-B6E6-C3A2CFBCB625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="189">
   <si>
     <t>광고 계정 마스터 (네이버/메타 공용)</t>
   </si>
@@ -700,13 +700,17 @@
   <si>
     <t>대성소파</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>핵이득마켓 GFA</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -777,6 +781,13 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -832,7 +843,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -880,6 +891,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -890,10 +905,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1035,6 +1047,60 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1045C7F9-BDCD-ED0B-0DB8-915D314D4623}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>257175</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44673611-78CC-A981-439A-D9858C785DE1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1249,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1267,55 +1333,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -4028,7 +4094,7 @@
       <c r="B72" t="s">
         <v>121</v>
       </c>
-      <c r="C72" s="21" t="s">
+      <c r="C72" s="17" t="s">
         <v>184</v>
       </c>
       <c r="D72" s="6" t="s">
@@ -4043,7 +4109,7 @@
       <c r="G72">
         <v>530852</v>
       </c>
-      <c r="J72" s="22" t="s">
+      <c r="J72" s="18" t="s">
         <v>187</v>
       </c>
       <c r="K72" s="6" t="s">
@@ -4060,7 +4126,7 @@
       <c r="B73" t="s">
         <v>185</v>
       </c>
-      <c r="C73" s="21" t="s">
+      <c r="C73" s="17" t="s">
         <v>186</v>
       </c>
       <c r="D73" s="6" t="s">
@@ -4075,7 +4141,7 @@
       <c r="G73">
         <v>122788</v>
       </c>
-      <c r="J73" s="21" t="s">
+      <c r="J73" s="17" t="s">
         <v>186</v>
       </c>
       <c r="K73" s="6" t="s">
@@ -4085,6 +4151,38 @@
         <v>23</v>
       </c>
       <c r="M73" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B74" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="C74" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="D74" t="s">
+        <v>80</v>
+      </c>
+      <c r="E74" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" t="s">
+        <v>146</v>
+      </c>
+      <c r="G74">
+        <v>3688863</v>
+      </c>
+      <c r="J74" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M74" s="6" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4096,7 +4194,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="L5:L1000 G71 D5:D1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D5:D1000 G71 L5:L1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E5:E1000" xr:uid="{00000000-0002-0000-0000-000001000000}">

--- a/account_master.xlsx
+++ b/account_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plano\OneDrive\바탕 화면\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7E785BC-40B8-4DA2-B6E6-C3A2CFBCB625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2525CE00-00CF-4C70-94B2-6E2344242213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="191">
   <si>
     <t>광고 계정 마스터 (네이버/메타 공용)</t>
   </si>
@@ -703,6 +703,13 @@
   </si>
   <si>
     <t>핵이득마켓 GFA</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>다온스테이</t>
+  </si>
+  <si>
+    <t>다온스테이</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -895,6 +902,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -905,7 +913,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1136,6 +1143,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>257175</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB2052C0-AFEF-A896-F9F3-0D9A28F5F94D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1315,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1333,55 +1394,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -4091,6 +4152,9 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="B72" t="s">
         <v>121</v>
       </c>
@@ -4123,6 +4187,9 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A73" s="6" t="s">
+        <v>78</v>
+      </c>
       <c r="B73" t="s">
         <v>185</v>
       </c>
@@ -4155,16 +4222,19 @@
       </c>
     </row>
     <row r="74" spans="1:14" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B74" s="23" t="s">
+      <c r="A74" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F74" t="s">
@@ -4173,7 +4243,7 @@
       <c r="G74">
         <v>3688863</v>
       </c>
-      <c r="J74" s="23" t="s">
+      <c r="J74" s="19" t="s">
         <v>188</v>
       </c>
       <c r="K74" s="6" t="s">
@@ -4185,6 +4255,44 @@
       <c r="M74" s="6" t="s">
         <v>80</v>
       </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B75" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75">
+        <v>2615032</v>
+      </c>
+      <c r="J75" t="s">
+        <v>189</v>
+      </c>
+      <c r="K75" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A76" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
